--- a/Data sets/SG/Sabaragamuwa/BUFFALO_DROUGHT_SAB_V1_upload_template.xlsx
+++ b/Data sets/SG/Sabaragamuwa/BUFFALO_DROUGHT_SAB_V1_upload_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nmmilinda/Downloads/SG/Sabaragamuwa/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nmmilinda/Projects/Risk-Radar_GGGI/Data sets/SG/Sabaragamuwa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5BAB2B3-5167-0545-BA25-2627353C437B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD62EED-A261-364F-92B3-4B7CE2AAC8BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-36100" yWindow="3760" windowWidth="35580" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4620" yWindow="600" windowWidth="39300" windowHeight="19100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2021-2025" sheetId="1" r:id="rId1"/>
@@ -1715,10 +1715,10 @@
       <c r="F2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="3" t="s">
         <v>188</v>
       </c>
       <c r="I2" s="3" t="s">
